--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/1750000/Output_0_15.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/1750000/Output_0_15.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>716371.8036446579</v>
+        <v>716379.1415249447</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>925658.2446351743</v>
+        <v>925399.3994514379</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18327269.62422525</v>
+        <v>18327015.93006068</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5283567.215382136</v>
+        <v>5283674.776931893</v>
       </c>
     </row>
     <row r="11">
@@ -646,10 +646,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -664,10 +664,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -706,16 +706,16 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.79691042959408</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="3">
@@ -728,13 +728,13 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D3" t="n">
-        <v>20.99531631735417</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>157.6450804554009</v>
+        <v>36.81406643968054</v>
       </c>
       <c r="F3" t="n">
         <v>145.0692123933839</v>
@@ -773,10 +773,10 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -788,7 +788,7 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -825,7 +825,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>14.83685490770588</v>
+        <v>17.55829564281241</v>
       </c>
       <c r="J4" t="n">
         <v>93.35918011667277</v>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -883,31 +883,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="F5" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.796910429594305</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -952,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>63.847659665762</v>
+        <v>29.79900896488251</v>
       </c>
       <c r="U6" t="n">
         <v>225.9413820809748</v>
@@ -1025,10 +1025,10 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W6" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1062,13 +1062,13 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>133.186967585368</v>
+        <v>17.55829564281241</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1174,22 +1174,22 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>202.2821007854552</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X8" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y8" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="9">
@@ -1202,25 +1202,25 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>62.88143347497287</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1250,22 +1250,22 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>84.01605654325938</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1293,19 +1293,19 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>110.9174757594852</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1363,16 +1363,16 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1402,7 +1402,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1417,16 +1417,16 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>84.01605654325947</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1487,22 +1487,22 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>171.6831711038378</v>
+        <v>35.40726547353833</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V12" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W12" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X12" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1560,10 +1560,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>47.02492433367365</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1600,19 +1600,19 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E14" t="n">
-        <v>202.2821007854552</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H14" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1639,7 +1639,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1660,10 +1660,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1727,7 +1727,7 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T15" t="n">
-        <v>63.10106833950421</v>
+        <v>63.14223173826442</v>
       </c>
       <c r="U15" t="n">
         <v>225.9413820809748</v>
@@ -1736,7 +1736,7 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W15" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1797,10 +1797,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>47.02492433367365</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1849,10 +1849,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1876,7 +1876,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.79691042959408</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -1885,16 +1885,16 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="U17" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W17" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1958,13 +1958,13 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>200.1647286948216</v>
+        <v>29.79900896488251</v>
       </c>
       <c r="U18" t="n">
         <v>225.9413820809748</v>
@@ -1973,10 +1973,10 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X18" t="n">
-        <v>175.4616765958773</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -2004,49 +2004,49 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2077,22 +2077,22 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F20" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G20" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H20" t="n">
-        <v>241</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2128,7 +2128,7 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>190.3328114308427</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
@@ -2201,7 +2201,7 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
         <v>225.9413820809748</v>
@@ -2210,13 +2210,13 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X21" t="n">
-        <v>34.61951074852038</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>29.05241763862477</v>
       </c>
     </row>
     <row r="22">
@@ -2289,13 +2289,13 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -2314,13 +2314,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>212.2728000000579</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>5.877922149011282e-11</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2362,13 +2362,13 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2402,10 +2402,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0.7465913262578567</v>
@@ -2447,13 +2447,13 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y24" t="n">
-        <v>33.15216235543048</v>
+        <v>29.05241763862477</v>
       </c>
     </row>
     <row r="25">
@@ -2526,10 +2526,10 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="X25" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -2554,19 +2554,19 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G26" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2587,16 +2587,16 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>72.44362390346359</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2605,7 +2605,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -2624,7 +2624,7 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>81.90579899813859</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -2675,22 +2675,22 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X27" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y27" t="n">
-        <v>205.6826957773044</v>
+        <v>29.05241763862477</v>
       </c>
     </row>
     <row r="28">
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -2748,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2782,10 +2782,10 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>212.2728000000016</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -2797,13 +2797,13 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>3.739472731467685e-11</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2824,7 +2824,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -2836,19 +2836,19 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>190.3453970742849</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2882,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2915,19 +2915,19 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9413820809748</v>
+        <v>49.3111039422953</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X30" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y30" t="n">
-        <v>29.75784556612239</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="31">
@@ -2991,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3006,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3016,22 +3016,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>190.3453970742846</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="G32" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3040,7 +3040,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -3061,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3073,13 +3073,13 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
@@ -3104,16 +3104,16 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3149,19 +3149,19 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>200.1647286948216</v>
+        <v>66.11861112998577</v>
       </c>
       <c r="U33" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>145.0020322390672</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="X33" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -3237,7 +3237,7 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="H35" t="n">
-        <v>21.15688084963966</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>11.19305615617947</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3313,7 +3313,7 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>29.7578455661223</v>
+        <v>29.1427070647978</v>
       </c>
       <c r="U36" t="n">
         <v>225.9413820809748</v>
@@ -3395,13 +3395,13 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W36" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="X36" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="37">
@@ -3423,7 +3423,7 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -3477,7 +3477,7 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -3499,13 +3499,13 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -3535,28 +3535,28 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>102.2970636939287</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>212.2853856434422</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>29.05241763862461</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -3632,13 +3632,13 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W39" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="X39" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y39" t="n">
-        <v>29.75784556612239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3648,25 +3648,25 @@
         </is>
       </c>
       <c r="B40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="C40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -3739,13 +3739,13 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="I41" t="n">
         <v>210.4758895704059</v>
@@ -3772,22 +3772,22 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.79691042959408</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>124.948886300959</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3857,22 +3857,22 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>29.1427070647978</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>50.01653186979276</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W42" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="X42" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
         <v>205.6826957773044</v>
@@ -3885,7 +3885,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -4015,25 +4015,25 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>11.16618163507844</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
     </row>
     <row r="45">
@@ -4049,13 +4049,13 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E45" t="n">
-        <v>109.3235678765929</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>145.0692123933839</v>
+        <v>106.988878104098</v>
       </c>
       <c r="G45" t="n">
         <v>137.3435171632106</v>
@@ -4106,7 +4106,7 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -4176,16 +4176,16 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0</v>
       </c>
       <c r="X46" t="n">
         <v>0</v>
@@ -4289,76 +4289,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>718.7505955256626</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C2" t="n">
-        <v>475.3162520913191</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D2" t="n">
-        <v>475.3162520913191</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E2" t="n">
-        <v>475.3162520913191</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F2" t="n">
-        <v>475.3162520913191</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G2" t="n">
-        <v>475.3162520913191</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H2" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K2" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L2" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M2" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N2" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O2" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P2" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q2" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R2" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S2" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T2" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U2" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V2" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="W2" t="n">
-        <v>964</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="X2" t="n">
-        <v>964</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="Y2" t="n">
-        <v>962.184938960006</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="3">
@@ -4368,76 +4368,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>689.4131260035546</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="C3" t="n">
-        <v>689.4131260035546</v>
+        <v>546.1553495854092</v>
       </c>
       <c r="D3" t="n">
-        <v>668.2057357840049</v>
+        <v>546.1553495854092</v>
       </c>
       <c r="E3" t="n">
-        <v>508.9682807785495</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F3" t="n">
-        <v>362.4337228054344</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G3" t="n">
-        <v>223.7028973880499</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H3" t="n">
-        <v>110.3337617956292</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I3" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J3" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K3" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L3" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M3" t="n">
-        <v>234.7819638733197</v>
+        <v>257.8852890990952</v>
       </c>
       <c r="N3" t="n">
-        <v>473.3719638733197</v>
+        <v>496.4894350879777</v>
       </c>
       <c r="O3" t="n">
-        <v>711.9619638733197</v>
+        <v>735.0935810768601</v>
       </c>
       <c r="P3" t="n">
-        <v>894.6054414866707</v>
+        <v>917.7370586902109</v>
       </c>
       <c r="Q3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R3" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S3" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T3" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U3" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V3" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W3" t="n">
-        <v>689.4131260035546</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="X3" t="n">
-        <v>689.4131260035546</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="Y3" t="n">
-        <v>689.4131260035546</v>
+        <v>720.6083788665362</v>
       </c>
     </row>
     <row r="4">
@@ -4447,76 +4447,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="H4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="I4" t="n">
-        <v>136.0766383258138</v>
+        <v>136.0777814360265</v>
       </c>
       <c r="J4" t="n">
-        <v>41.77443618776046</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="K4" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L4" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M4" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N4" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="5">
@@ -4526,76 +4526,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>964.0000000000002</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="C5" t="n">
-        <v>964.0000000000002</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="D5" t="n">
-        <v>964.0000000000002</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="E5" t="n">
-        <v>964.0000000000002</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F5" t="n">
-        <v>720.5656565656568</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G5" t="n">
-        <v>477.1313131313134</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H5" t="n">
-        <v>233.6969696969699</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I5" t="n">
-        <v>21.09506103999425</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J5" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K5" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L5" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M5" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N5" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O5" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P5" t="n">
-        <v>964.0000000000002</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q5" t="n">
-        <v>964.0000000000002</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R5" t="n">
-        <v>964.0000000000002</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S5" t="n">
-        <v>964.0000000000002</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T5" t="n">
-        <v>964.0000000000002</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U5" t="n">
-        <v>964.0000000000002</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V5" t="n">
-        <v>964.0000000000002</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W5" t="n">
-        <v>964.0000000000002</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X5" t="n">
-        <v>964.0000000000002</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y5" t="n">
-        <v>964.0000000000002</v>
+        <v>720.6083788665362</v>
       </c>
     </row>
     <row r="6">
@@ -4605,76 +4605,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C6" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D6" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E6" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F6" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G6" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H6" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I6" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J6" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K6" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L6" t="n">
-        <v>249.2431058683491</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M6" t="n">
-        <v>304.1765223866491</v>
+        <v>257.8852890990952</v>
       </c>
       <c r="N6" t="n">
-        <v>542.7665223866492</v>
+        <v>496.4894350879777</v>
       </c>
       <c r="O6" t="n">
-        <v>781.3565223866492</v>
+        <v>735.0935810768601</v>
       </c>
       <c r="P6" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S6" t="n">
-        <v>790.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T6" t="n">
-        <v>726.0900699296972</v>
+        <v>933.9571464551993</v>
       </c>
       <c r="U6" t="n">
-        <v>497.8664516660862</v>
+        <v>705.7335281915883</v>
       </c>
       <c r="V6" t="n">
-        <v>262.7143434343434</v>
+        <v>470.5814199598456</v>
       </c>
       <c r="W6" t="n">
-        <v>19.28</v>
+        <v>227.1326433157456</v>
       </c>
       <c r="X6" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y6" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="7">
@@ -4684,76 +4684,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="H7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="I7" t="n">
-        <v>19.28</v>
+        <v>136.0777814360265</v>
       </c>
       <c r="J7" t="n">
-        <v>19.28</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="K7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L7" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M7" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N7" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="8">
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C8" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D8" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E8" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F8" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G8" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H8" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I8" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J8" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K8" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L8" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M8" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N8" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O8" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P8" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q8" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R8" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S8" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T8" t="n">
-        <v>953.9083846317729</v>
+        <v>749.627473042513</v>
       </c>
       <c r="U8" t="n">
-        <v>953.9083846317729</v>
+        <v>749.627473042513</v>
       </c>
       <c r="V8" t="n">
-        <v>749.5830303030303</v>
+        <v>749.627473042513</v>
       </c>
       <c r="W8" t="n">
-        <v>506.1486868686869</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="X8" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="Y8" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C9" t="n">
-        <v>19.28</v>
+        <v>789.6041262295092</v>
       </c>
       <c r="D9" t="n">
-        <v>19.28</v>
+        <v>640.669716568258</v>
       </c>
       <c r="E9" t="n">
-        <v>19.28</v>
+        <v>481.4322615628025</v>
       </c>
       <c r="F9" t="n">
-        <v>19.28</v>
+        <v>334.8977035896875</v>
       </c>
       <c r="G9" t="n">
-        <v>19.28</v>
+        <v>196.166878172303</v>
       </c>
       <c r="H9" t="n">
-        <v>19.28</v>
+        <v>82.7977425798823</v>
       </c>
       <c r="I9" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J9" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K9" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L9" t="n">
-        <v>249.2431058683491</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M9" t="n">
-        <v>487.8331058683492</v>
+        <v>304.2053859195205</v>
       </c>
       <c r="N9" t="n">
-        <v>725.41</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O9" t="n">
-        <v>964</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S9" t="n">
-        <v>790.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T9" t="n">
-        <v>790.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U9" t="n">
-        <v>705.717951871619</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V9" t="n">
-        <v>470.5658436398763</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W9" t="n">
-        <v>227.1315002055328</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X9" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y9" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G10" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="H10" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="I10" t="n">
-        <v>19.28</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="J10" t="n">
-        <v>19.28</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="K10" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L10" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M10" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N10" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19.28</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="C11" t="n">
-        <v>19.28</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="D11" t="n">
-        <v>19.28</v>
+        <v>710.516763498309</v>
       </c>
       <c r="E11" t="n">
-        <v>19.28</v>
+        <v>467.067986854209</v>
       </c>
       <c r="F11" t="n">
-        <v>19.28</v>
+        <v>223.6192102101089</v>
       </c>
       <c r="G11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K11" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L11" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M11" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N11" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O11" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P11" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q11" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R11" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S11" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T11" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U11" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V11" t="n">
-        <v>720.5656565656566</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="W11" t="n">
-        <v>477.1313131313132</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="X11" t="n">
-        <v>233.6969696969697</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="Y11" t="n">
-        <v>19.28</v>
+        <v>953.9655401424092</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>104.14470357905</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C12" t="n">
-        <v>104.14470357905</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D12" t="n">
-        <v>104.14470357905</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L12" t="n">
-        <v>249.2431058683491</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M12" t="n">
-        <v>304.1765223866491</v>
+        <v>486.8488635328713</v>
       </c>
       <c r="N12" t="n">
-        <v>542.7665223866492</v>
+        <v>725.4530095217538</v>
       </c>
       <c r="O12" t="n">
-        <v>781.3565223866492</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P12" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q12" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R12" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S12" t="n">
-        <v>790.5826554506689</v>
+        <v>928.2922408909005</v>
       </c>
       <c r="T12" t="n">
-        <v>790.5826554506689</v>
+        <v>726.1056462496665</v>
       </c>
       <c r="U12" t="n">
-        <v>790.5826554506689</v>
+        <v>497.8820279860555</v>
       </c>
       <c r="V12" t="n">
-        <v>555.4305472189262</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="W12" t="n">
-        <v>311.9962037845828</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X12" t="n">
-        <v>104.14470357905</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y12" t="n">
-        <v>104.14470357905</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L13" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M13" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N13" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O13" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P13" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q13" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="R13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y13" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>467.0396977630861</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C14" t="n">
-        <v>467.0396977630861</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="D14" t="n">
-        <v>467.0396977630861</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="E14" t="n">
-        <v>262.7143434343434</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="F14" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G14" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H14" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I14" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J14" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K14" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L14" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M14" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N14" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O14" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P14" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q14" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R14" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S14" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T14" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U14" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V14" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W14" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X14" t="n">
-        <v>710.4740411974295</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y14" t="n">
-        <v>467.0396977630861</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="C15" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D15" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E15" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F15" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G15" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H15" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I15" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J15" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K15" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L15" t="n">
-        <v>374.6006659261865</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M15" t="n">
-        <v>542.7665223866492</v>
+        <v>486.8488635328713</v>
       </c>
       <c r="N15" t="n">
-        <v>542.7665223866492</v>
+        <v>725.4530095217538</v>
       </c>
       <c r="O15" t="n">
-        <v>781.3565223866492</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S15" t="n">
-        <v>790.5826554506689</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="T15" t="n">
-        <v>726.8442025824828</v>
+        <v>726.8597789024521</v>
       </c>
       <c r="U15" t="n">
-        <v>498.6205843188719</v>
+        <v>498.6361606388412</v>
       </c>
       <c r="V15" t="n">
-        <v>263.4684760871291</v>
+        <v>263.4840524070985</v>
       </c>
       <c r="W15" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="X15" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="Y15" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I16" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J16" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K16" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L16" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M16" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N16" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q16" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="R16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>475.3162520913191</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C17" t="n">
-        <v>475.3162520913191</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D17" t="n">
-        <v>475.3162520913191</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E17" t="n">
-        <v>475.3162520913191</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F17" t="n">
-        <v>475.3162520913191</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G17" t="n">
-        <v>475.3162520913191</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H17" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I17" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J17" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K17" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L17" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M17" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N17" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O17" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P17" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q17" t="n">
-        <v>962.184938960006</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R17" t="n">
-        <v>962.184938960006</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S17" t="n">
-        <v>962.184938960006</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T17" t="n">
-        <v>962.184938960006</v>
+        <v>749.627473042513</v>
       </c>
       <c r="U17" t="n">
-        <v>718.7505955256626</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="V17" t="n">
-        <v>718.7505955256626</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="W17" t="n">
-        <v>475.3162520913191</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X17" t="n">
-        <v>475.3162520913191</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y17" t="n">
-        <v>475.3162520913191</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K18" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L18" t="n">
-        <v>374.6006659261865</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M18" t="n">
-        <v>374.6006659261865</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N18" t="n">
-        <v>542.7665223866492</v>
+        <v>726.4525409563269</v>
       </c>
       <c r="O18" t="n">
-        <v>781.3565223866492</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P18" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q18" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R18" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S18" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T18" t="n">
-        <v>660.6438759116518</v>
+        <v>933.9571464551993</v>
       </c>
       <c r="U18" t="n">
-        <v>432.4202576480408</v>
+        <v>705.7335281915883</v>
       </c>
       <c r="V18" t="n">
-        <v>197.2681494162981</v>
+        <v>470.5814199598456</v>
       </c>
       <c r="W18" t="n">
-        <v>197.2681494162981</v>
+        <v>227.1326433157456</v>
       </c>
       <c r="X18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C19" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D19" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E19" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F19" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L19" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M19" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N19" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U19" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V19" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W19" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X19" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y19" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>761.6530195501136</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C20" t="n">
-        <v>761.6530195501136</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="D20" t="n">
-        <v>761.6530195501136</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="E20" t="n">
-        <v>761.6530195501136</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="F20" t="n">
-        <v>518.2186761157702</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="G20" t="n">
-        <v>274.7843326814268</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="H20" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I20" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R20" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S20" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T20" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U20" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V20" t="n">
-        <v>761.6530195501136</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W20" t="n">
-        <v>761.6530195501136</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X20" t="n">
-        <v>761.6530195501136</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y20" t="n">
-        <v>761.6530195501136</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="C21" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D21" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E21" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F21" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G21" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H21" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I21" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>19.28</v>
+        <v>74.24228005117135</v>
       </c>
       <c r="L21" t="n">
-        <v>249.2431058683491</v>
+        <v>304.2053859195205</v>
       </c>
       <c r="M21" t="n">
-        <v>304.1765223866491</v>
+        <v>542.809531908403</v>
       </c>
       <c r="N21" t="n">
-        <v>542.7665223866492</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O21" t="n">
-        <v>781.3565223866492</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T21" t="n">
-        <v>761.813405358766</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U21" t="n">
-        <v>533.5897870951551</v>
+        <v>735.8335372470253</v>
       </c>
       <c r="V21" t="n">
-        <v>298.4376788634124</v>
+        <v>500.6814290152826</v>
       </c>
       <c r="W21" t="n">
-        <v>55.00333542906893</v>
+        <v>257.2326523711826</v>
       </c>
       <c r="X21" t="n">
-        <v>20.03413265278571</v>
+        <v>49.38115216564972</v>
       </c>
       <c r="Y21" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L22" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M22" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N22" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O22" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P22" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q22" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R22" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S22" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T22" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U22" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V22" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W22" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X22" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>477.1313131313716</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C23" t="n">
-        <v>477.1313131313716</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="D23" t="n">
-        <v>477.1313131313716</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="E23" t="n">
-        <v>233.6969696970282</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="F23" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J23" t="n">
-        <v>19.27999999994063</v>
+        <v>19.28114311021275</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2389935105573</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3148450952159</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.29047235812</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.1449945653594</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O23" t="n">
-        <v>874.3399447080075</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P23" t="n">
-        <v>964.0000000000584</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q23" t="n">
-        <v>964.0000000000584</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R23" t="n">
-        <v>964.0000000000584</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S23" t="n">
-        <v>964.0000000000584</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T23" t="n">
-        <v>964.0000000000584</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U23" t="n">
-        <v>720.565656565715</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V23" t="n">
-        <v>477.1313131313716</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W23" t="n">
-        <v>477.1313131313716</v>
+        <v>749.627473042513</v>
       </c>
       <c r="X23" t="n">
-        <v>477.1313131313716</v>
+        <v>749.627473042513</v>
       </c>
       <c r="Y23" t="n">
-        <v>477.1313131313716</v>
+        <v>749.627473042513</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>223.7028973880499</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="C24" t="n">
-        <v>223.7028973880499</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D24" t="n">
-        <v>223.7028973880499</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E24" t="n">
-        <v>223.7028973880499</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F24" t="n">
-        <v>223.7028973880499</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G24" t="n">
-        <v>223.7028973880499</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H24" t="n">
-        <v>110.3337617956292</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I24" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L24" t="n">
-        <v>374.6006659261865</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M24" t="n">
-        <v>374.6006659261865</v>
+        <v>234.810827406191</v>
       </c>
       <c r="N24" t="n">
-        <v>473.3719638733197</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O24" t="n">
-        <v>711.9619638733197</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P24" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U24" t="n">
-        <v>735.7763817363891</v>
+        <v>735.8335372470253</v>
       </c>
       <c r="V24" t="n">
-        <v>500.6242735046464</v>
+        <v>500.6814290152826</v>
       </c>
       <c r="W24" t="n">
-        <v>257.1899300703029</v>
+        <v>257.2326523711826</v>
       </c>
       <c r="X24" t="n">
-        <v>257.1899300703029</v>
+        <v>49.38115216564972</v>
       </c>
       <c r="Y24" t="n">
-        <v>223.7028973880499</v>
+        <v>20.03527576299844</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="C25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="D25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="E25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L25" t="n">
-        <v>46.59412500771298</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M25" t="n">
-        <v>85.78216319993516</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N25" t="n">
-        <v>129.4730138553714</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O25" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P25" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q25" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R25" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S25" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T25" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U25" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V25" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W25" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="X25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="Y25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>518.2186761157702</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C26" t="n">
-        <v>518.2186761157702</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="D26" t="n">
-        <v>518.2186761157702</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="E26" t="n">
-        <v>518.2186761157702</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="F26" t="n">
-        <v>518.2186761157702</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G26" t="n">
-        <v>274.7843326814268</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H26" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I26" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.3399447079652</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964.0000000000161</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>953.9083846317891</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R26" t="n">
-        <v>802.5254372164864</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S26" t="n">
-        <v>591.3940537960365</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T26" t="n">
-        <v>518.2186761157702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U26" t="n">
-        <v>518.2186761157702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V26" t="n">
-        <v>518.2186761157702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W26" t="n">
-        <v>518.2186761157702</v>
+        <v>749.627473042513</v>
       </c>
       <c r="X26" t="n">
-        <v>518.2186761157702</v>
+        <v>749.627473042513</v>
       </c>
       <c r="Y26" t="n">
-        <v>518.2186761157702</v>
+        <v>749.627473042513</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>102.7672629539358</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="C27" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D27" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E27" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F27" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G27" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H27" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I27" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L27" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M27" t="n">
-        <v>487.8331058683492</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="N27" t="n">
-        <v>542.7665223866492</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O27" t="n">
-        <v>781.3565223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P27" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T27" t="n">
-        <v>761.813405358766</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U27" t="n">
-        <v>761.813405358766</v>
+        <v>735.8335372470253</v>
       </c>
       <c r="V27" t="n">
-        <v>761.813405358766</v>
+        <v>500.6814290152826</v>
       </c>
       <c r="W27" t="n">
-        <v>518.3790619244226</v>
+        <v>257.2326523711826</v>
       </c>
       <c r="X27" t="n">
-        <v>310.5275617188897</v>
+        <v>49.38115216564972</v>
       </c>
       <c r="Y27" t="n">
-        <v>102.7672629539358</v>
+        <v>20.03527576299844</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C28" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="D28" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="E28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L28" t="n">
-        <v>46.59412500771298</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M28" t="n">
-        <v>85.78216319993516</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N28" t="n">
-        <v>129.4730138553714</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O28" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P28" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q28" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R28" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S28" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T28" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U28" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V28" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W28" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X28" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y28" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>233.6969696969713</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="C29" t="n">
-        <v>19.28</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="D29" t="n">
-        <v>19.28</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="E29" t="n">
-        <v>19.28</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="F29" t="n">
-        <v>19.28</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="G29" t="n">
-        <v>19.28</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="H29" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="I29" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J29" t="n">
-        <v>19.27999999996223</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2389935105005</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3148450951591</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M29" t="n">
-        <v>519.2904723580632</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N29" t="n">
-        <v>725.1449945653026</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O29" t="n">
-        <v>874.3399447079506</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P29" t="n">
-        <v>964.0000000000016</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q29" t="n">
-        <v>964.0000000000016</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R29" t="n">
-        <v>964.0000000000016</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S29" t="n">
-        <v>964.0000000000016</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T29" t="n">
-        <v>964.0000000000016</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U29" t="n">
-        <v>964.0000000000016</v>
+        <v>761.6974622895962</v>
       </c>
       <c r="V29" t="n">
-        <v>964.0000000000016</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="W29" t="n">
-        <v>720.5656565656582</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="X29" t="n">
-        <v>477.1313131313148</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="Y29" t="n">
-        <v>233.6969696969713</v>
+        <v>518.2486856454962</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="C30" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D30" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E30" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F30" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G30" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H30" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I30" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K30" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L30" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M30" t="n">
-        <v>304.1765223866491</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="N30" t="n">
-        <v>542.7665223866492</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O30" t="n">
-        <v>781.3565223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P30" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U30" t="n">
-        <v>735.7763817363891</v>
+        <v>914.2479596093278</v>
       </c>
       <c r="V30" t="n">
-        <v>500.6242735046464</v>
+        <v>679.0958513775852</v>
       </c>
       <c r="W30" t="n">
-        <v>257.1899300703029</v>
+        <v>435.6470747334852</v>
       </c>
       <c r="X30" t="n">
-        <v>49.33842986477009</v>
+        <v>227.7955745279523</v>
       </c>
       <c r="Y30" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L31" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M31" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N31" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X31" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>262.7143434343434</v>
+        <v>710.5167634983089</v>
       </c>
       <c r="C32" t="n">
-        <v>262.7143434343434</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="D32" t="n">
-        <v>262.7143434343434</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="E32" t="n">
-        <v>262.7143434343434</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="F32" t="n">
-        <v>262.7143434343434</v>
+        <v>31.35113235729607</v>
       </c>
       <c r="G32" t="n">
-        <v>19.28</v>
+        <v>31.35113235729607</v>
       </c>
       <c r="H32" t="n">
-        <v>19.28</v>
+        <v>31.35113235729607</v>
       </c>
       <c r="I32" t="n">
-        <v>19.28</v>
+        <v>31.35113235729607</v>
       </c>
       <c r="J32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K32" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L32" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M32" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N32" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759371</v>
       </c>
       <c r="O32" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185851</v>
       </c>
       <c r="P32" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Q32" t="n">
-        <v>964</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="R32" t="n">
-        <v>964</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="S32" t="n">
-        <v>964</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="T32" t="n">
-        <v>964</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="U32" t="n">
-        <v>720.5656565656566</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="V32" t="n">
-        <v>506.1486868686869</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="W32" t="n">
-        <v>262.7143434343434</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="X32" t="n">
-        <v>262.7143434343434</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="Y32" t="n">
-        <v>262.7143434343434</v>
+        <v>953.9655401424089</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>179.2715876582412</v>
+        <v>418.6697947459187</v>
       </c>
       <c r="C33" t="n">
-        <v>179.2715876582412</v>
+        <v>418.6697947459187</v>
       </c>
       <c r="D33" t="n">
-        <v>179.2715876582412</v>
+        <v>418.6697947459187</v>
       </c>
       <c r="E33" t="n">
-        <v>20.03413265278571</v>
+        <v>418.6697947459187</v>
       </c>
       <c r="F33" t="n">
-        <v>20.03413265278571</v>
+        <v>272.1352367728036</v>
       </c>
       <c r="G33" t="n">
-        <v>20.03413265278571</v>
+        <v>133.4044113554191</v>
       </c>
       <c r="H33" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="I33" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="J33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K33" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L33" t="n">
-        <v>249.2431058683491</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="M33" t="n">
-        <v>487.8331058683492</v>
+        <v>234.8108274061909</v>
       </c>
       <c r="N33" t="n">
-        <v>542.7665223866492</v>
+        <v>473.4149733950733</v>
       </c>
       <c r="O33" t="n">
-        <v>781.3565223866492</v>
+        <v>712.0191193839557</v>
       </c>
       <c r="P33" t="n">
-        <v>964</v>
+        <v>894.6625969973067</v>
       </c>
       <c r="Q33" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R33" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="S33" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="T33" t="n">
-        <v>761.813405358766</v>
+        <v>897.2706796217615</v>
       </c>
       <c r="U33" t="n">
-        <v>533.5897870951551</v>
+        <v>897.2706796217615</v>
       </c>
       <c r="V33" t="n">
-        <v>387.1230878637741</v>
+        <v>662.1185713900187</v>
       </c>
       <c r="W33" t="n">
-        <v>387.1230878637741</v>
+        <v>418.6697947459187</v>
       </c>
       <c r="X33" t="n">
-        <v>179.2715876582412</v>
+        <v>418.6697947459187</v>
       </c>
       <c r="Y33" t="n">
-        <v>179.2715876582412</v>
+        <v>418.6697947459187</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C34" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D34" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E34" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F34" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G34" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H34" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I34" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J34" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K34" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L34" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M34" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N34" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O34" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P34" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q34" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R34" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S34" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T34" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U34" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V34" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W34" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X34" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y34" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>284.0849301511512</v>
+        <v>274.0360370837869</v>
       </c>
       <c r="C35" t="n">
-        <v>284.0849301511512</v>
+        <v>274.0360370837869</v>
       </c>
       <c r="D35" t="n">
-        <v>284.0849301511512</v>
+        <v>274.0360370837869</v>
       </c>
       <c r="E35" t="n">
-        <v>284.0849301511512</v>
+        <v>274.0360370837869</v>
       </c>
       <c r="F35" t="n">
-        <v>284.0849301511512</v>
+        <v>274.0360370837869</v>
       </c>
       <c r="G35" t="n">
-        <v>40.65058671680774</v>
+        <v>30.58726043968693</v>
       </c>
       <c r="H35" t="n">
-        <v>19.28</v>
+        <v>30.58726043968693</v>
       </c>
       <c r="I35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K35" t="n">
-        <v>122.2389935105155</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L35" t="n">
-        <v>302.3148450951741</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M35" t="n">
-        <v>519.2904723580782</v>
+        <v>519.3476278686976</v>
       </c>
       <c r="N35" t="n">
-        <v>725.1449945653176</v>
+        <v>725.202150075937</v>
       </c>
       <c r="O35" t="n">
-        <v>874.3399447079656</v>
+        <v>874.397100218585</v>
       </c>
       <c r="P35" t="n">
-        <v>964.0000000000166</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Q35" t="n">
-        <v>964.0000000000166</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="R35" t="n">
-        <v>964.0000000000166</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="S35" t="n">
-        <v>752.8686165795667</v>
+        <v>742.8341567219591</v>
       </c>
       <c r="T35" t="n">
-        <v>527.5192735854946</v>
+        <v>517.4848137278869</v>
       </c>
       <c r="U35" t="n">
-        <v>527.5192735854946</v>
+        <v>517.4848137278869</v>
       </c>
       <c r="V35" t="n">
-        <v>284.0849301511512</v>
+        <v>274.0360370837869</v>
       </c>
       <c r="W35" t="n">
-        <v>284.0849301511512</v>
+        <v>274.0360370837869</v>
       </c>
       <c r="X35" t="n">
-        <v>284.0849301511512</v>
+        <v>274.0360370837869</v>
       </c>
       <c r="Y35" t="n">
-        <v>284.0849301511512</v>
+        <v>274.0360370837869</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="C36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="D36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="E36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="F36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="G36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="H36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="I36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="J36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K36" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L36" t="n">
-        <v>249.2431058683491</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="M36" t="n">
-        <v>473.3719638733197</v>
+        <v>383.2428491569325</v>
       </c>
       <c r="N36" t="n">
-        <v>473.3719638733197</v>
+        <v>473.4149733950733</v>
       </c>
       <c r="O36" t="n">
-        <v>711.9619638733197</v>
+        <v>712.0191193839557</v>
       </c>
       <c r="P36" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973067</v>
       </c>
       <c r="Q36" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R36" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="S36" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="T36" t="n">
-        <v>933.94157013523</v>
+        <v>934.6200776674059</v>
       </c>
       <c r="U36" t="n">
-        <v>705.717951871619</v>
+        <v>706.396459403795</v>
       </c>
       <c r="V36" t="n">
-        <v>470.5658436398763</v>
+        <v>471.2443511720523</v>
       </c>
       <c r="W36" t="n">
-        <v>227.1315002055328</v>
+        <v>227.7955745279523</v>
       </c>
       <c r="X36" t="n">
-        <v>19.28</v>
+        <v>227.7955745279523</v>
       </c>
       <c r="Y36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>829.4677095097293</v>
+        <v>964.057155510636</v>
       </c>
       <c r="C37" t="n">
-        <v>829.4677095097293</v>
+        <v>964.057155510636</v>
       </c>
       <c r="D37" t="n">
-        <v>829.4677095097293</v>
+        <v>964.057155510636</v>
       </c>
       <c r="E37" t="n">
-        <v>829.4677095097293</v>
+        <v>964.057155510636</v>
       </c>
       <c r="F37" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="G37" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="H37" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="I37" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="J37" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="K37" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="L37" t="n">
-        <v>856.7818345174422</v>
+        <v>856.8389900280782</v>
       </c>
       <c r="M37" t="n">
-        <v>895.9698727096644</v>
+        <v>896.0270282203004</v>
       </c>
       <c r="N37" t="n">
-        <v>939.6607233651007</v>
+        <v>939.7178788757367</v>
       </c>
       <c r="O37" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="P37" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Q37" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R37" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="S37" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="T37" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="U37" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="V37" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="W37" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="X37" t="n">
-        <v>829.4677095097293</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Y37" t="n">
-        <v>829.4677095097293</v>
+        <v>964.057155510636</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>19.28</v>
+        <v>749.6274730425127</v>
       </c>
       <c r="C38" t="n">
-        <v>19.28</v>
+        <v>749.6274730425127</v>
       </c>
       <c r="D38" t="n">
-        <v>19.28</v>
+        <v>749.6274730425127</v>
       </c>
       <c r="E38" t="n">
-        <v>19.28</v>
+        <v>506.1786963984127</v>
       </c>
       <c r="F38" t="n">
-        <v>19.28</v>
+        <v>262.7299197543127</v>
       </c>
       <c r="G38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K38" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L38" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M38" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N38" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O38" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P38" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q38" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R38" t="n">
-        <v>802.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S38" t="n">
-        <v>591.3940537960203</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T38" t="n">
-        <v>366.0447108019482</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U38" t="n">
-        <v>366.0447108019482</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V38" t="n">
-        <v>122.6103673676048</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W38" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X38" t="n">
-        <v>19.28</v>
+        <v>749.6274730425127</v>
       </c>
       <c r="Y38" t="n">
-        <v>19.28</v>
+        <v>749.6274730425127</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="C39" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="D39" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="E39" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="F39" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="G39" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="H39" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="I39" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="J39" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K39" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L39" t="n">
-        <v>249.2431058683491</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M39" t="n">
-        <v>304.1765223866491</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N39" t="n">
-        <v>542.7665223866492</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="O39" t="n">
-        <v>781.3565223866492</v>
+        <v>712.0191193839557</v>
       </c>
       <c r="P39" t="n">
-        <v>964</v>
+        <v>894.6625969973067</v>
       </c>
       <c r="Q39" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R39" t="n">
-        <v>964</v>
+        <v>934.7112791079849</v>
       </c>
       <c r="S39" t="n">
-        <v>964</v>
+        <v>934.7112791079849</v>
       </c>
       <c r="T39" t="n">
-        <v>964</v>
+        <v>934.7112791079849</v>
       </c>
       <c r="U39" t="n">
-        <v>735.7763817363891</v>
+        <v>706.487660844374</v>
       </c>
       <c r="V39" t="n">
-        <v>500.6242735046464</v>
+        <v>471.3355526126313</v>
       </c>
       <c r="W39" t="n">
-        <v>257.1899300703029</v>
+        <v>227.8867759685313</v>
       </c>
       <c r="X39" t="n">
-        <v>49.33842986477009</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="Y39" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C40" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D40" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E40" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F40" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G40" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="H40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L40" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M40" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N40" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O40" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P40" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q40" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R40" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S40" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T40" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U40" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V40" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W40" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X40" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y40" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>718.7505955256626</v>
+        <v>475.3318284112884</v>
       </c>
       <c r="C41" t="n">
-        <v>718.7505955256626</v>
+        <v>475.3318284112884</v>
       </c>
       <c r="D41" t="n">
-        <v>718.7505955256626</v>
+        <v>475.3318284112884</v>
       </c>
       <c r="E41" t="n">
-        <v>718.7505955256626</v>
+        <v>475.3318284112884</v>
       </c>
       <c r="F41" t="n">
-        <v>475.3162520913191</v>
+        <v>475.3318284112884</v>
       </c>
       <c r="G41" t="n">
-        <v>231.8819086569757</v>
+        <v>475.3318284112884</v>
       </c>
       <c r="H41" t="n">
-        <v>231.8819086569757</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="I41" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J41" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K41" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L41" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M41" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N41" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759371</v>
       </c>
       <c r="O41" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185851</v>
       </c>
       <c r="P41" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Q41" t="n">
-        <v>962.184938960006</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R41" t="n">
-        <v>962.184938960006</v>
+        <v>812.6742080953333</v>
       </c>
       <c r="S41" t="n">
-        <v>962.184938960006</v>
+        <v>601.5428246748834</v>
       </c>
       <c r="T41" t="n">
-        <v>962.184938960006</v>
+        <v>475.3318284112884</v>
       </c>
       <c r="U41" t="n">
-        <v>962.184938960006</v>
+        <v>475.3318284112884</v>
       </c>
       <c r="V41" t="n">
-        <v>718.7505955256626</v>
+        <v>475.3318284112884</v>
       </c>
       <c r="W41" t="n">
-        <v>718.7505955256626</v>
+        <v>475.3318284112884</v>
       </c>
       <c r="X41" t="n">
-        <v>718.7505955256626</v>
+        <v>475.3318284112884</v>
       </c>
       <c r="Y41" t="n">
-        <v>718.7505955256626</v>
+        <v>475.3318284112884</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="C42" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="D42" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="E42" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="F42" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="G42" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="H42" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="I42" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="J42" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K42" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L42" t="n">
-        <v>374.6006659261865</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M42" t="n">
-        <v>374.6006659261865</v>
+        <v>473.4149733950733</v>
       </c>
       <c r="N42" t="n">
-        <v>542.7665223866492</v>
+        <v>473.4149733950733</v>
       </c>
       <c r="O42" t="n">
-        <v>781.3565223866492</v>
+        <v>712.0191193839557</v>
       </c>
       <c r="P42" t="n">
-        <v>964</v>
+        <v>894.6625969973067</v>
       </c>
       <c r="Q42" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R42" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="S42" t="n">
-        <v>964</v>
+        <v>934.6200776674059</v>
       </c>
       <c r="T42" t="n">
-        <v>964</v>
+        <v>934.6200776674059</v>
       </c>
       <c r="U42" t="n">
-        <v>913.478250636573</v>
+        <v>706.396459403795</v>
       </c>
       <c r="V42" t="n">
-        <v>678.3261424048302</v>
+        <v>471.2443511720523</v>
       </c>
       <c r="W42" t="n">
-        <v>434.8917989704868</v>
+        <v>227.7955745279523</v>
       </c>
       <c r="X42" t="n">
-        <v>227.0402987649539</v>
+        <v>227.7955745279523</v>
       </c>
       <c r="Y42" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C43" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D43" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E43" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F43" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G43" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H43" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I43" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J43" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K43" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L43" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M43" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N43" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O43" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P43" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q43" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R43" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S43" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T43" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U43" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V43" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W43" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X43" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y43" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="44">
@@ -7607,76 +7607,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K44" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211349</v>
       </c>
       <c r="L44" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057935</v>
       </c>
       <c r="M44" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686976</v>
       </c>
       <c r="N44" t="n">
-        <v>725.144994565301</v>
+        <v>725.202150075937</v>
       </c>
       <c r="O44" t="n">
-        <v>874.339944707949</v>
+        <v>874.397100218585</v>
       </c>
       <c r="P44" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Q44" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="R44" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="S44" t="n">
-        <v>742.7770012113231</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="T44" t="n">
-        <v>517.427658217251</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="U44" t="n">
-        <v>273.9933147829075</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="V44" t="n">
-        <v>30.55897134856409</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="W44" t="n">
-        <v>19.28</v>
+        <v>749.6274730425127</v>
       </c>
       <c r="X44" t="n">
-        <v>19.28</v>
+        <v>506.1786963984127</v>
       </c>
       <c r="Y44" t="n">
-        <v>19.28</v>
+        <v>262.7299197543127</v>
       </c>
     </row>
     <row r="45">
@@ -7686,76 +7686,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>619.3961271185423</v>
+        <v>619.4388494194217</v>
       </c>
       <c r="C45" t="n">
-        <v>619.3961271185423</v>
+        <v>619.4388494194217</v>
       </c>
       <c r="D45" t="n">
-        <v>619.3961271185423</v>
+        <v>470.5044397581704</v>
       </c>
       <c r="E45" t="n">
-        <v>508.9682807785495</v>
+        <v>470.5044397581704</v>
       </c>
       <c r="F45" t="n">
-        <v>362.4337228054344</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G45" t="n">
-        <v>223.7028973880499</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H45" t="n">
-        <v>110.3337617956292</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I45" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="J45" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K45" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L45" t="n">
-        <v>19.28</v>
+        <v>374.6018090363992</v>
       </c>
       <c r="M45" t="n">
-        <v>234.7819638733197</v>
+        <v>486.8488635328711</v>
       </c>
       <c r="N45" t="n">
-        <v>473.3719638733197</v>
+        <v>725.4530095217535</v>
       </c>
       <c r="O45" t="n">
-        <v>711.9619638733197</v>
+        <v>964.057155510636</v>
       </c>
       <c r="P45" t="n">
-        <v>894.6054414866707</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Q45" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R45" t="n">
-        <v>862.8304705528857</v>
+        <v>862.8876260635217</v>
       </c>
       <c r="S45" t="n">
-        <v>862.8304705528857</v>
+        <v>862.8876260635217</v>
       </c>
       <c r="T45" t="n">
-        <v>862.8304705528857</v>
+        <v>862.8876260635217</v>
       </c>
       <c r="U45" t="n">
-        <v>862.8304705528857</v>
+        <v>862.8876260635217</v>
       </c>
       <c r="V45" t="n">
-        <v>862.8304705528857</v>
+        <v>862.8876260635217</v>
       </c>
       <c r="W45" t="n">
-        <v>619.3961271185423</v>
+        <v>619.4388494194217</v>
       </c>
       <c r="X45" t="n">
-        <v>619.3961271185423</v>
+        <v>619.4388494194217</v>
       </c>
       <c r="Y45" t="n">
-        <v>619.3961271185423</v>
+        <v>619.4388494194217</v>
       </c>
     </row>
     <row r="46">
@@ -7765,76 +7765,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>19.28</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="C46" t="n">
-        <v>19.28</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="D46" t="n">
-        <v>19.28</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="E46" t="n">
-        <v>19.28</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="F46" t="n">
-        <v>19.28</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="G46" t="n">
-        <v>19.28</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="H46" t="n">
-        <v>19.28</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="I46" t="n">
-        <v>19.28</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="J46" t="n">
-        <v>19.28</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="K46" t="n">
-        <v>19.28</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="L46" t="n">
-        <v>46.59412500771298</v>
+        <v>856.8389900280782</v>
       </c>
       <c r="M46" t="n">
-        <v>85.78216319993516</v>
+        <v>896.0270282203004</v>
       </c>
       <c r="N46" t="n">
-        <v>129.4730138553714</v>
+        <v>939.7178788757367</v>
       </c>
       <c r="O46" t="n">
-        <v>153.8122904902707</v>
+        <v>964.057155510636</v>
       </c>
       <c r="P46" t="n">
-        <v>153.8122904902707</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Q46" t="n">
-        <v>153.8122904902707</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R46" t="n">
-        <v>153.8122904902707</v>
+        <v>964.057155510636</v>
       </c>
       <c r="S46" t="n">
-        <v>153.8122904902707</v>
+        <v>964.057155510636</v>
       </c>
       <c r="T46" t="n">
-        <v>19.28</v>
+        <v>964.057155510636</v>
       </c>
       <c r="U46" t="n">
-        <v>19.28</v>
+        <v>964.057155510636</v>
       </c>
       <c r="V46" t="n">
-        <v>19.28</v>
+        <v>964.057155510636</v>
       </c>
       <c r="W46" t="n">
-        <v>19.28</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="X46" t="n">
-        <v>19.28</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="Y46" t="n">
-        <v>19.28</v>
+        <v>829.5248650203653</v>
       </c>
     </row>
   </sheetData>
@@ -7962,7 +7962,7 @@
         <v>324.1454125711647</v>
       </c>
       <c r="L2" t="n">
-        <v>417.6046363682045</v>
+        <v>417.6612145504504</v>
       </c>
       <c r="M2" t="n">
         <v>449.5135334928325</v>
@@ -8044,19 +8044,19 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M3" t="n">
-        <v>359.81278530921</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N3" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O3" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P3" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q3" t="n">
-        <v>210.0772877358491</v>
+        <v>186.7697506723097</v>
       </c>
       <c r="R3" t="n">
         <v>45.52166981132082</v>
@@ -8211,7 +8211,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P5" t="n">
-        <v>321.742129989237</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q5" t="n">
         <v>212.3149906599047</v>
@@ -8278,22 +8278,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L6" t="n">
-        <v>370.8403453034592</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M6" t="n">
-        <v>197.6223334354527</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N6" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O6" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P6" t="n">
-        <v>318.4627686399372</v>
+        <v>295.1552315763977</v>
       </c>
       <c r="Q6" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R6" t="n">
         <v>45.52166981132082</v>
@@ -8433,7 +8433,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K8" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L8" t="n">
         <v>417.6612145504504</v>
@@ -8518,16 +8518,16 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M9" t="n">
-        <v>383.1340339220183</v>
+        <v>197.6503338623806</v>
       </c>
       <c r="N9" t="n">
-        <v>371.3183728223746</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O9" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P9" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q9" t="n">
         <v>139.9817740860215</v>
@@ -8670,7 +8670,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K11" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L11" t="n">
         <v>417.6612145504504</v>
@@ -8755,16 +8755,16 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M12" t="n">
-        <v>197.6223334354527</v>
+        <v>382.1386950879875</v>
       </c>
       <c r="N12" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O12" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P12" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q12" t="n">
         <v>139.9817740860215</v>
@@ -8907,7 +8907,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K14" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L14" t="n">
         <v>417.6612145504504</v>
@@ -8986,22 +8986,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K15" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L15" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M15" t="n">
-        <v>311.9985353972331</v>
+        <v>382.1386950879875</v>
       </c>
       <c r="N15" t="n">
-        <v>131.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O15" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P15" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q15" t="n">
         <v>139.9817740860215</v>
@@ -9144,7 +9144,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L17" t="n">
         <v>417.6612145504504</v>
@@ -9223,22 +9223,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K18" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L18" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M18" t="n">
-        <v>142.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N18" t="n">
-        <v>301.2062135585481</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O18" t="n">
-        <v>383.5962444444444</v>
+        <v>382.6009056104135</v>
       </c>
       <c r="P18" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q18" t="n">
         <v>139.9817740860215</v>
@@ -9381,7 +9381,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L20" t="n">
         <v>417.6612145504504</v>
@@ -9460,19 +9460,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K21" t="n">
-        <v>137.841438974359</v>
+        <v>193.3577389147212</v>
       </c>
       <c r="L21" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M21" t="n">
-        <v>197.6223334354527</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N21" t="n">
-        <v>372.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O21" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P21" t="n">
         <v>318.4627686399372</v>
@@ -9618,7 +9618,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>324.0888343890379</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L23" t="n">
         <v>417.6612145504504</v>
@@ -9697,19 +9697,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L24" t="n">
-        <v>370.8403453034592</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M24" t="n">
-        <v>142.1340339220183</v>
+        <v>359.8407857361378</v>
       </c>
       <c r="N24" t="n">
-        <v>231.1106999087204</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O24" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P24" t="n">
         <v>318.4627686399372</v>
@@ -9867,7 +9867,7 @@
         <v>437.3469244119842</v>
       </c>
       <c r="O26" t="n">
-        <v>380.7436030805158</v>
+        <v>380.8001812627454</v>
       </c>
       <c r="P26" t="n">
         <v>321.7987081714826</v>
@@ -9934,25 +9934,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K27" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L27" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M27" t="n">
-        <v>383.1340339220183</v>
+        <v>241.9453110519923</v>
       </c>
       <c r="N27" t="n">
-        <v>186.8300115967677</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O27" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P27" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q27" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10092,7 +10092,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>324.0888343889586</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L29" t="n">
         <v>417.6612145504504</v>
@@ -10171,25 +10171,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K30" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L30" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M30" t="n">
-        <v>197.6223334354527</v>
+        <v>241.9453110519923</v>
       </c>
       <c r="N30" t="n">
-        <v>372.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O30" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P30" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q30" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10329,7 +10329,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K32" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L32" t="n">
         <v>417.6612145504504</v>
@@ -10408,25 +10408,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K33" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L33" t="n">
-        <v>370.8403453034592</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M33" t="n">
-        <v>383.1340339220183</v>
+        <v>233.2169876979181</v>
       </c>
       <c r="N33" t="n">
-        <v>186.8300115967677</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O33" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221034</v>
       </c>
       <c r="P33" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q33" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10566,7 +10566,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>324.0888343889356</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L35" t="n">
         <v>417.6612145504504</v>
@@ -10645,19 +10645,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K36" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L36" t="n">
-        <v>370.8403453034592</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M36" t="n">
-        <v>368.526819785625</v>
+        <v>383.1483227996773</v>
       </c>
       <c r="N36" t="n">
-        <v>131.3417120833333</v>
+        <v>222.4246658592331</v>
       </c>
       <c r="O36" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221034</v>
       </c>
       <c r="P36" t="n">
         <v>318.4627686399372</v>
@@ -10806,7 +10806,7 @@
         <v>324.1454125711647</v>
       </c>
       <c r="L38" t="n">
-        <v>417.6046363682045</v>
+        <v>417.6612145504504</v>
       </c>
       <c r="M38" t="n">
         <v>449.5135334928325</v>
@@ -10888,19 +10888,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M39" t="n">
-        <v>197.6223334354527</v>
+        <v>383.1483227996773</v>
       </c>
       <c r="N39" t="n">
-        <v>372.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O39" t="n">
-        <v>383.5962444444444</v>
+        <v>369.0313196126378</v>
       </c>
       <c r="P39" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q39" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -11040,7 +11040,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L41" t="n">
         <v>417.6612145504504</v>
@@ -11119,25 +11119,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K42" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L42" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M42" t="n">
-        <v>142.1340339220183</v>
+        <v>368.5691090902117</v>
       </c>
       <c r="N42" t="n">
-        <v>301.2062135585481</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O42" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221034</v>
       </c>
       <c r="P42" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q42" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11277,10 +11277,10 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K44" t="n">
-        <v>324.1454125711647</v>
+        <v>324.1454125711646</v>
       </c>
       <c r="L44" t="n">
-        <v>417.6046363682045</v>
+        <v>417.6612145504504</v>
       </c>
       <c r="M44" t="n">
         <v>449.5135334928325</v>
@@ -11356,25 +11356,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K45" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L45" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M45" t="n">
-        <v>359.81278530921</v>
+        <v>255.5148970497677</v>
       </c>
       <c r="N45" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O45" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221034</v>
       </c>
       <c r="P45" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q45" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R45" t="n">
         <v>45.52166981132082</v>
@@ -22504,10 +22504,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>141.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C2" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D2" t="n">
         <v>354.683041620683</v>
@@ -22522,10 +22522,10 @@
         <v>415.302737515135</v>
       </c>
       <c r="H2" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J2" t="n">
         <v>11.94928935461252</v>
@@ -22564,16 +22564,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V2" t="n">
-        <v>327.7522584701349</v>
+        <v>115.4668728266929</v>
       </c>
       <c r="W2" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X2" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y2" t="n">
-        <v>384.4410282264595</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="3">
@@ -22586,13 +22586,13 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C3" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>126.4497492472846</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>120.8310140157204</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -22631,10 +22631,10 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T3" t="n">
         <v>200.1647286948216</v>
@@ -22646,7 +22646,7 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W3" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X3" t="n">
         <v>205.7729852034775</v>
@@ -22683,7 +22683,7 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I4" t="n">
-        <v>140.6136200195524</v>
+        <v>137.8921792844459</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -22704,7 +22704,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q4" t="n">
         <v>86.16204325169439</v>
@@ -22741,31 +22741,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C5" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D5" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E5" t="n">
-        <v>381.9303700722618</v>
+        <v>169.6449844288197</v>
       </c>
       <c r="F5" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G5" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H5" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J5" t="n">
-        <v>10.15237892501821</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -22810,7 +22810,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y5" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="6">
@@ -22871,10 +22871,10 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T6" t="n">
-        <v>136.3170690290596</v>
+        <v>170.3657197299391</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -22883,10 +22883,10 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X6" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>205.6826957773044</v>
@@ -22920,13 +22920,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I7" t="n">
-        <v>22.26350734189026</v>
+        <v>137.8921792844459</v>
       </c>
       <c r="J7" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -23023,7 +23023,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R8" t="n">
         <v>149.8691179411497</v>
@@ -23032,22 +23032,22 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T8" t="n">
-        <v>223.0958495641314</v>
+        <v>10.81046392068936</v>
       </c>
       <c r="U8" t="n">
         <v>251.3456529078365</v>
       </c>
       <c r="V8" t="n">
-        <v>125.4701576846797</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W8" t="n">
-        <v>108.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X8" t="n">
-        <v>128.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y8" t="n">
-        <v>145.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="9">
@@ -23060,25 +23060,25 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C9" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>89.39663285141508</v>
+        <v>26.5151993764422</v>
       </c>
       <c r="J9" t="n">
         <v>0.7465913262578567</v>
@@ -23108,22 +23108,22 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T9" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U9" t="n">
-        <v>141.9253255377154</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W9" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y9" t="n">
         <v>205.6826957773044</v>
@@ -23151,19 +23151,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G10" t="n">
-        <v>167.9909793584588</v>
+        <v>57.07350359897357</v>
       </c>
       <c r="H10" t="n">
         <v>162.2271725074396</v>
       </c>
       <c r="I10" t="n">
-        <v>22.26350734189026</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J10" t="n">
         <v>93.35918011667277</v>
       </c>
       <c r="K10" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -23221,16 +23221,16 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D11" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E11" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F11" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G11" t="n">
-        <v>415.302737515135</v>
+        <v>213.0080510862378</v>
       </c>
       <c r="H11" t="n">
         <v>339.4748021157671</v>
@@ -23260,7 +23260,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>149.8691179411497</v>
@@ -23275,16 +23275,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V11" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W11" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X11" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y11" t="n">
-        <v>173.9651386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="12">
@@ -23303,7 +23303,7 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E12" t="n">
-        <v>73.62902391214148</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F12" t="n">
         <v>145.0692123933839</v>
@@ -23345,22 +23345,22 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>136.2759056302995</v>
       </c>
       <c r="T12" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y12" t="n">
         <v>205.6826957773044</v>
@@ -23394,7 +23394,7 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I13" t="n">
-        <v>22.26350734189026</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J13" t="n">
         <v>93.35918011667277</v>
@@ -23418,10 +23418,10 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>177.2933913771695</v>
+        <v>130.2684670434958</v>
       </c>
       <c r="S13" t="n">
         <v>224.0165980369723</v>
@@ -23458,19 +23458,19 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D14" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E14" t="n">
-        <v>179.6482692868065</v>
+        <v>169.6449844288197</v>
       </c>
       <c r="F14" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G14" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H14" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I14" t="n">
         <v>210.4758895704059</v>
@@ -23497,7 +23497,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R14" t="n">
         <v>149.8691179411497</v>
@@ -23518,10 +23518,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X14" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y14" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="15">
@@ -23585,7 +23585,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>137.0636603553174</v>
+        <v>137.0224969565572</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -23594,7 +23594,7 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X15" t="n">
         <v>205.7729852034775</v>
@@ -23631,7 +23631,7 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I16" t="n">
-        <v>22.26350734189026</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J16" t="n">
         <v>93.35918011667277</v>
@@ -23655,10 +23655,10 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q16" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>177.2933913771695</v>
+        <v>130.2684670434958</v>
       </c>
       <c r="S16" t="n">
         <v>224.0165980369723</v>
@@ -23707,10 +23707,10 @@
         <v>415.302737515135</v>
       </c>
       <c r="H17" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J17" t="n">
         <v>11.94928935461252</v>
@@ -23734,7 +23734,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>8.193788784950724</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>149.8691179411497</v>
@@ -23743,16 +23743,16 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T17" t="n">
-        <v>223.0958495641314</v>
+        <v>20.80116313523413</v>
       </c>
       <c r="U17" t="n">
-        <v>10.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V17" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W17" t="n">
-        <v>108.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X17" t="n">
         <v>369.731100678469</v>
@@ -23792,7 +23792,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -23816,13 +23816,13 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S18" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>170.3657197299391</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -23831,10 +23831,10 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X18" t="n">
-        <v>30.31130860760021</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>205.6826957773044</v>
@@ -23862,7 +23862,7 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G19" t="n">
-        <v>34.80401177309074</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H19" t="n">
         <v>162.2271725074396</v>
@@ -23904,7 +23904,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U19" t="n">
-        <v>286.3190293564909</v>
+        <v>153.1320617711229</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23935,22 +23935,22 @@
         <v>354.683041620683</v>
       </c>
       <c r="E20" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F20" t="n">
-        <v>165.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G20" t="n">
-        <v>174.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H20" t="n">
-        <v>98.47480211576715</v>
+        <v>127.189416472325</v>
       </c>
       <c r="I20" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -23971,7 +23971,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
         <v>149.8691179411497</v>
@@ -23986,7 +23986,7 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V20" t="n">
-        <v>137.4194470392922</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W20" t="n">
         <v>349.240968717413</v>
@@ -24059,7 +24059,7 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -24068,13 +24068,13 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X21" t="n">
-        <v>171.1534744549571</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>205.6826957773044</v>
+        <v>176.6302781386796</v>
       </c>
     </row>
     <row r="22">
@@ -24147,13 +24147,13 @@
         <v>252.137643323828</v>
       </c>
       <c r="W22" t="n">
-        <v>286.522998336591</v>
+        <v>153.336030751223</v>
       </c>
       <c r="X22" t="n">
         <v>225.7096553890372</v>
       </c>
       <c r="Y22" t="n">
-        <v>85.39768576672677</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="23">
@@ -24163,7 +24163,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C23" t="n">
         <v>365.2728917710076</v>
@@ -24172,13 +24172,13 @@
         <v>354.683041620683</v>
       </c>
       <c r="E23" t="n">
-        <v>140.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F23" t="n">
-        <v>194.6032457416536</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G23" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H23" t="n">
         <v>339.4748021157671</v>
@@ -24187,7 +24187,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J23" t="n">
-        <v>11.94928935455374</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -24220,13 +24220,13 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U23" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V23" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W23" t="n">
-        <v>349.240968717413</v>
+        <v>136.955583073971</v>
       </c>
       <c r="X23" t="n">
         <v>369.731100678469</v>
@@ -24260,10 +24260,10 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -24305,13 +24305,13 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X24" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>172.5305334218739</v>
+        <v>176.6302781386796</v>
       </c>
     </row>
     <row r="25">
@@ -24384,10 +24384,10 @@
         <v>252.137643323828</v>
       </c>
       <c r="W25" t="n">
-        <v>286.522998336591</v>
+        <v>153.336030751223</v>
       </c>
       <c r="X25" t="n">
-        <v>92.52268780366913</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y25" t="n">
         <v>218.5846533520948</v>
@@ -24400,7 +24400,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C26" t="n">
         <v>365.2728917710076</v>
@@ -24412,19 +24412,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F26" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G26" t="n">
-        <v>174.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H26" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I26" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -24445,16 +24445,16 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T26" t="n">
-        <v>150.6522256606678</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U26" t="n">
         <v>251.3456529078365</v>
@@ -24463,7 +24463,7 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W26" t="n">
-        <v>349.240968717413</v>
+        <v>136.955583073971</v>
       </c>
       <c r="X26" t="n">
         <v>369.731100678469</v>
@@ -24482,7 +24482,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C27" t="n">
-        <v>90.80269999017715</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D27" t="n">
         <v>147.4450655646388</v>
@@ -24533,22 +24533,22 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U27" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>176.6302781386796</v>
       </c>
     </row>
     <row r="28">
@@ -24567,7 +24567,7 @@
         <v>148.6154730182124</v>
       </c>
       <c r="E28" t="n">
-        <v>146.4339626465692</v>
+        <v>13.24699506120118</v>
       </c>
       <c r="F28" t="n">
         <v>145.4210480229312</v>
@@ -24606,7 +24606,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R28" t="n">
-        <v>44.10642379180146</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S28" t="n">
         <v>224.0165980369723</v>
@@ -24640,10 +24640,10 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C29" t="n">
-        <v>153.000091771006</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D29" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E29" t="n">
         <v>381.9303700722618</v>
@@ -24655,13 +24655,13 @@
         <v>415.302737515135</v>
       </c>
       <c r="H29" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I29" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J29" t="n">
-        <v>11.94928935457512</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -24682,7 +24682,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>149.8691179411497</v>
@@ -24694,19 +24694,19 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U29" t="n">
-        <v>251.3456529078365</v>
+        <v>61.00025583355162</v>
       </c>
       <c r="V29" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W29" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X29" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y29" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="30">
@@ -24740,7 +24740,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -24773,19 +24773,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>176.6302781386795</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>175.924850211182</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -24849,7 +24849,7 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T31" t="n">
-        <v>227.9455894282815</v>
+        <v>94.75862184291347</v>
       </c>
       <c r="U31" t="n">
         <v>286.3190293564909</v>
@@ -24864,7 +24864,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y31" t="n">
-        <v>85.39768576672677</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="32">
@@ -24874,22 +24874,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858216</v>
       </c>
       <c r="C32" t="n">
-        <v>365.2728917710076</v>
+        <v>174.9274946967229</v>
       </c>
       <c r="D32" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E32" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946028</v>
       </c>
       <c r="F32" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G32" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H32" t="n">
         <v>339.4748021157671</v>
@@ -24898,7 +24898,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J32" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -24919,7 +24919,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>149.8691179411497</v>
@@ -24931,13 +24931,13 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U32" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V32" t="n">
-        <v>115.4794584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W32" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X32" t="n">
         <v>369.731100678469</v>
@@ -24962,16 +24962,16 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F33" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>89.39663285141508</v>
@@ -25007,19 +25007,19 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>134.0461175648358</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V33" t="n">
-        <v>87.79855491035806</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326061</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y33" t="n">
         <v>205.6826957773044</v>
@@ -25041,7 +25041,7 @@
         <v>148.6154730182124</v>
       </c>
       <c r="E34" t="n">
-        <v>146.4339626465692</v>
+        <v>13.24699506120115</v>
       </c>
       <c r="F34" t="n">
         <v>145.4210480229312</v>
@@ -25095,7 +25095,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W34" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X34" t="n">
         <v>225.7096553890372</v>
@@ -25126,13 +25126,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>174.302737515135</v>
+        <v>174.2884486374761</v>
       </c>
       <c r="H35" t="n">
-        <v>318.3179212661275</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I35" t="n">
-        <v>210.4758895704059</v>
+        <v>199.2828334142264</v>
       </c>
       <c r="J35" t="n">
         <v>11.94928935461252</v>
@@ -25156,7 +25156,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>149.8691179411497</v>
@@ -25171,7 +25171,7 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V35" t="n">
-        <v>86.7522584701349</v>
+        <v>86.73796959247591</v>
       </c>
       <c r="W35" t="n">
         <v>349.240968717413</v>
@@ -25214,7 +25214,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -25244,7 +25244,7 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T36" t="n">
-        <v>170.4068831286993</v>
+        <v>171.0220216300238</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -25253,13 +25253,13 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326061</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y36" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -25281,7 +25281,7 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F37" t="n">
-        <v>145.4210480229312</v>
+        <v>12.23408043756325</v>
       </c>
       <c r="G37" t="n">
         <v>167.9909793584588</v>
@@ -25335,7 +25335,7 @@
         <v>286.522998336591</v>
       </c>
       <c r="X37" t="n">
-        <v>92.52268780366913</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y37" t="n">
         <v>218.5846533520948</v>
@@ -25357,13 +25357,13 @@
         <v>354.683041620683</v>
       </c>
       <c r="E38" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946028</v>
       </c>
       <c r="F38" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G38" t="n">
-        <v>415.302737515135</v>
+        <v>174.2884486374761</v>
       </c>
       <c r="H38" t="n">
         <v>339.4748021157671</v>
@@ -25393,28 +25393,28 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U38" t="n">
         <v>251.3456529078365</v>
       </c>
       <c r="V38" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W38" t="n">
-        <v>246.9439050234843</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X38" t="n">
-        <v>369.731100678469</v>
+        <v>157.4457150350268</v>
       </c>
       <c r="Y38" t="n">
         <v>386.2379386560536</v>
@@ -25451,7 +25451,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J39" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -25475,7 +25475,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>100.1578341526431</v>
+        <v>71.10541651401851</v>
       </c>
       <c r="S39" t="n">
         <v>171.6831711038378</v>
@@ -25490,13 +25490,13 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326061</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>175.924850211182</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="40">
@@ -25506,7 +25506,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>46.64501259656927</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C40" t="n">
         <v>167.2468210986278</v>
@@ -25524,7 +25524,7 @@
         <v>167.9909793584588</v>
       </c>
       <c r="H40" t="n">
-        <v>162.2271725074396</v>
+        <v>29.04020492207155</v>
       </c>
       <c r="I40" t="n">
         <v>155.4504749272583</v>
@@ -25597,13 +25597,13 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F41" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H41" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810815</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25630,22 +25630,22 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>8.193788784950724</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>223.0958495641314</v>
+        <v>98.14696326317237</v>
       </c>
       <c r="U41" t="n">
         <v>251.3456529078365</v>
       </c>
       <c r="V41" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W41" t="n">
         <v>349.240968717413</v>
@@ -25688,7 +25688,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -25715,22 +25715,22 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S42" t="n">
-        <v>171.6831711038378</v>
+        <v>142.54046403904</v>
       </c>
       <c r="T42" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U42" t="n">
-        <v>175.924850211182</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326061</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -25743,7 +25743,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>179.8319801819373</v>
+        <v>46.64501259656927</v>
       </c>
       <c r="C43" t="n">
         <v>167.2468210986278</v>
@@ -25812,7 +25812,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y43" t="n">
-        <v>85.39768576672677</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="44">
@@ -25822,7 +25822,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858216</v>
       </c>
       <c r="C44" t="n">
         <v>365.2728917710076</v>
@@ -25873,25 +25873,25 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U44" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V44" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W44" t="n">
-        <v>338.0747870823346</v>
+        <v>146.9462822885158</v>
       </c>
       <c r="X44" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y44" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783946</v>
       </c>
     </row>
     <row r="45">
@@ -25907,13 +25907,13 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D45" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>48.32151257880807</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>38.08033428928586</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -25964,7 +25964,7 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W45" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326061</v>
       </c>
       <c r="X45" t="n">
         <v>205.7729852034775</v>
@@ -26034,7 +26034,7 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T46" t="n">
-        <v>94.75862184291347</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U46" t="n">
         <v>286.3190293564909</v>
@@ -26043,7 +26043,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W46" t="n">
-        <v>286.522998336591</v>
+        <v>153.336030751223</v>
       </c>
       <c r="X46" t="n">
         <v>225.7096553890372</v>
@@ -26078,7 +26078,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>456932.547341795</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
     <row r="3">
@@ -26086,7 +26086,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>456932.547341795</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
     <row r="4">
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>456932.5473417949</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>456932.5473417949</v>
+        <v>456941.8494611644</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>456932.547341795</v>
+        <v>456941.8494611644</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>456932.5473417949</v>
+        <v>456941.8494611642</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>456932.5473417949</v>
+        <v>456941.8494611644</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>456932.5473418078</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>456932.5473417968</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>456932.5473417992</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>456932.5473417949</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>456932.5473417967</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>456932.5473417949</v>
+        <v>456941.8494611642</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>456932.547341795</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>456932.547341795</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
   </sheetData>
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>124617.9674568532</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="C2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="D2" t="n">
-        <v>124617.9674568532</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="E2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="F2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="G2" t="n">
-        <v>124617.9674568532</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="H2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="I2" t="n">
-        <v>124617.9674568566</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="J2" t="n">
-        <v>124617.9674568537</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="K2" t="n">
-        <v>124617.9674568543</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="L2" t="n">
-        <v>124617.9674568532</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="M2" t="n">
-        <v>124617.9674568536</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="N2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="O2" t="n">
-        <v>124617.9674568532</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="P2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
     </row>
     <row r="3">
@@ -26313,7 +26313,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80764.643</v>
+        <v>80769.43153154773</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -26337,7 +26337,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>63056.204</v>
+        <v>63059.94259910623</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="C4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="D4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="E4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="F4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="G4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="H4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="I4" t="n">
-        <v>179.5221438966301</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="J4" t="n">
-        <v>179.5221438966178</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="K4" t="n">
-        <v>179.5221438966206</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="L4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="M4" t="n">
-        <v>179.5221438966179</v>
+        <v>179.5324977039668</v>
       </c>
       <c r="N4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="O4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="P4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039668</v>
       </c>
     </row>
     <row r="5">
@@ -26417,49 +26417,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376167</v>
       </c>
       <c r="C5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376167</v>
       </c>
       <c r="D5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376167</v>
       </c>
       <c r="E5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="F5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="G5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="L5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="M5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="N5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="O5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="P5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-4606.597687043432</v>
+        <v>-4609.728394514081</v>
       </c>
       <c r="C6" t="n">
-        <v>76158.0453129565</v>
+        <v>76159.70313703368</v>
       </c>
       <c r="D6" t="n">
-        <v>76158.04531295656</v>
+        <v>76159.70313703365</v>
       </c>
       <c r="E6" t="n">
-        <v>109785.6453129565</v>
+        <v>109787.3031370336</v>
       </c>
       <c r="F6" t="n">
-        <v>109785.6453129565</v>
+        <v>109787.3031370336</v>
       </c>
       <c r="G6" t="n">
-        <v>109785.6453129565</v>
+        <v>109787.3031370337</v>
       </c>
       <c r="H6" t="n">
-        <v>109785.6453129565</v>
+        <v>109787.3031370337</v>
       </c>
       <c r="I6" t="n">
-        <v>109785.6453129599</v>
+        <v>109787.3031370336</v>
       </c>
       <c r="J6" t="n">
-        <v>46729.44131295706</v>
+        <v>46727.36053792742</v>
       </c>
       <c r="K6" t="n">
-        <v>109785.6453129577</v>
+        <v>109787.3031370337</v>
       </c>
       <c r="L6" t="n">
-        <v>109785.6453129565</v>
+        <v>109787.3031370337</v>
       </c>
       <c r="M6" t="n">
-        <v>109785.645312957</v>
+        <v>109787.3031370336</v>
       </c>
       <c r="N6" t="n">
-        <v>109785.6453129565</v>
+        <v>109787.3031370337</v>
       </c>
       <c r="O6" t="n">
-        <v>109785.6453129565</v>
+        <v>109787.3031370337</v>
       </c>
       <c r="P6" t="n">
-        <v>109785.6453129565</v>
+        <v>109787.3031370336</v>
       </c>
     </row>
   </sheetData>
@@ -26727,49 +26727,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="L4" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="M4" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="N4" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="O4" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="P4" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
     </row>
   </sheetData>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26898,43 +26898,43 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,49 +26944,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27185,7 +27185,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -34617,13 +34617,13 @@
         <v>104.0555615261842</v>
       </c>
       <c r="L2" t="n">
-        <v>181.8382213982173</v>
+        <v>181.8947995804632</v>
       </c>
       <c r="M2" t="n">
         <v>219.1673002655598</v>
       </c>
       <c r="N2" t="n">
-        <v>207.9338608153932</v>
+        <v>207.9338608153933</v>
       </c>
       <c r="O2" t="n">
         <v>150.7019698410586</v>
@@ -34699,19 +34699,19 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>217.6787513871916</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N3" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O3" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P3" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q3" t="n">
-        <v>70.09551364982758</v>
+        <v>46.78797658628819</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -34866,7 +34866,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P5" t="n">
-        <v>90.5091342339674</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -34933,22 +34933,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>232.285965523585</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>55.48829951343433</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N6" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O6" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P6" t="n">
-        <v>184.4883612256069</v>
+        <v>161.1808241620674</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -35088,7 +35088,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L8" t="n">
         <v>181.8947995804632</v>
@@ -35173,16 +35173,16 @@
         <v>232.285965523585</v>
       </c>
       <c r="M9" t="n">
-        <v>241</v>
+        <v>55.51629994036225</v>
       </c>
       <c r="N9" t="n">
-        <v>239.9766607390412</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O9" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35325,7 +35325,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L11" t="n">
         <v>181.8947995804632</v>
@@ -35410,16 +35410,16 @@
         <v>232.285965523585</v>
       </c>
       <c r="M12" t="n">
-        <v>55.48829951343433</v>
+        <v>240.0046611659691</v>
       </c>
       <c r="N12" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O12" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P12" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -35562,7 +35562,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L14" t="n">
         <v>181.8947995804632</v>
@@ -35641,22 +35641,22 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M15" t="n">
-        <v>169.8645014752148</v>
+        <v>240.0046611659691</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O15" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P15" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -35799,7 +35799,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L17" t="n">
         <v>181.8947995804632</v>
@@ -35878,22 +35878,22 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N18" t="n">
-        <v>169.8645014752148</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O18" t="n">
-        <v>241</v>
+        <v>240.0046611659691</v>
       </c>
       <c r="P18" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -36036,7 +36036,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L20" t="n">
         <v>181.8947995804632</v>
@@ -36115,19 +36115,19 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>55.51629994036225</v>
       </c>
       <c r="L21" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M21" t="n">
-        <v>55.48829951343433</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N21" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P21" t="n">
         <v>184.4883612256069</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>103.9989833440573</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L23" t="n">
         <v>181.8947995804632</v>
@@ -36352,19 +36352,19 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>232.285965523585</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>217.7067518141195</v>
       </c>
       <c r="N24" t="n">
-        <v>99.76898782538704</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P24" t="n">
         <v>184.4883612256069</v>
@@ -36522,7 +36522,7 @@
         <v>207.9338608153932</v>
       </c>
       <c r="O26" t="n">
-        <v>150.645391658829</v>
+        <v>150.7019698410586</v>
       </c>
       <c r="P26" t="n">
         <v>90.5657124162131</v>
@@ -36589,25 +36589,25 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L27" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M27" t="n">
-        <v>241</v>
+        <v>99.81127712997396</v>
       </c>
       <c r="N27" t="n">
-        <v>55.48829951343436</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P27" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36747,7 +36747,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>103.998983343978</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L29" t="n">
         <v>181.8947995804632</v>
@@ -36826,25 +36826,25 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L30" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M30" t="n">
-        <v>55.48829951343433</v>
+        <v>99.81127712997396</v>
       </c>
       <c r="N30" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P30" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -36984,7 +36984,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L32" t="n">
         <v>181.8947995804632</v>
@@ -37063,25 +37063,25 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L33" t="n">
-        <v>232.285965523585</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>241</v>
+        <v>91.08295377589981</v>
       </c>
       <c r="N33" t="n">
-        <v>55.48829951343436</v>
+        <v>241.014288877659</v>
       </c>
       <c r="O33" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="P33" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37221,13 +37221,13 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>103.998983343955</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L35" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M35" t="n">
-        <v>219.1673002655598</v>
+        <v>219.1673002655595</v>
       </c>
       <c r="N35" t="n">
         <v>207.9338608153932</v>
@@ -37300,19 +37300,19 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L36" t="n">
-        <v>232.285965523585</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>226.3927858636066</v>
+        <v>241.014288877659</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>91.08295377589984</v>
       </c>
       <c r="O36" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="P36" t="n">
         <v>184.4883612256069</v>
@@ -37461,7 +37461,7 @@
         <v>104.0555615261842</v>
       </c>
       <c r="L38" t="n">
-        <v>181.8382213982173</v>
+        <v>181.8947995804632</v>
       </c>
       <c r="M38" t="n">
         <v>219.1673002655598</v>
@@ -37543,19 +37543,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M39" t="n">
-        <v>55.48829951343433</v>
+        <v>241.014288877659</v>
       </c>
       <c r="N39" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>241</v>
+        <v>226.4350751681934</v>
       </c>
       <c r="P39" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37695,7 +37695,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L41" t="n">
         <v>181.8947995804632</v>
@@ -37774,25 +37774,25 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>226.4350751681934</v>
       </c>
       <c r="N42" t="n">
-        <v>169.8645014752148</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="P42" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -37932,10 +37932,10 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>104.0555615261842</v>
+        <v>104.055561526184</v>
       </c>
       <c r="L44" t="n">
-        <v>181.8382213982173</v>
+        <v>181.8947995804632</v>
       </c>
       <c r="M44" t="n">
         <v>219.1673002655598</v>
@@ -38011,25 +38011,25 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M45" t="n">
-        <v>217.6787513871916</v>
+        <v>113.3808631277494</v>
       </c>
       <c r="N45" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="O45" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="P45" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
